--- a/excel_files/8.3.1.a.xlsx
+++ b/excel_files/8.3.1.a.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Национальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Национальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1FAE802-80F0-4AB8-A64E-88235BBCE979}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22755" windowHeight="7305"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -37,12 +38,6 @@
     <t>Средние предприятия</t>
   </si>
   <si>
-    <t>8.3.1.2 Доля занятых в малых и средних предприятиях от всего занятого населения в экономике</t>
-  </si>
-  <si>
-    <t>8.3.1.2 Share of employed in small and medium enterprises of the total employed population in the economy</t>
-  </si>
-  <si>
     <t>Small enterprises</t>
   </si>
   <si>
@@ -73,13 +68,19 @@
     <t>(in percent)</t>
   </si>
   <si>
-    <t>8.3.1.2 Экономикадагы иш менен камсыз болгон бардык калктын чакан жана орто ишканаларда иштегендердин үлүшү</t>
+    <t>8.3.1.a Share of employed in small and medium enterprises of the total employed population in the economy</t>
+  </si>
+  <si>
+    <t>8.3.1.a Доля занятых в малых и средних предприятиях от всего занятого населения в экономике</t>
+  </si>
+  <si>
+    <t>8.3.1.a Экономикадагы иш менен камсыз болгон бардык калктын чакан жана орто ишканаларда иштегендердин үлүшү</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -158,7 +159,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -175,6 +176,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -182,7 +194,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -214,18 +226,19 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Normal 17" xfId="1"/>
-    <cellStyle name="Normal 2" xfId="3"/>
+    <cellStyle name="Normal 17" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Normal 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 7" xfId="2"/>
+    <cellStyle name="Обычный 7" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -502,45 +515,37 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="38.42578125" style="2" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
     </row>
-    <row r="3" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -555,16 +560,17 @@
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
+      <c r="O3" s="12"/>
     </row>
-    <row r="4" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>10</v>
       </c>
       <c r="D4" s="6">
         <v>2013</v>
@@ -599,16 +605,19 @@
       <c r="N4" s="6">
         <v>2023</v>
       </c>
+      <c r="O4" s="13">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="5" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D5" s="8">
         <v>2.2999999999999998</v>
@@ -643,16 +652,19 @@
       <c r="N5" s="8">
         <v>2.5449890821474286</v>
       </c>
+      <c r="O5" s="14">
+        <v>2.8</v>
+      </c>
     </row>
-    <row r="6" spans="1:14" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>1</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" s="10">
         <v>1.6</v>
@@ -687,8 +699,11 @@
       <c r="N6" s="10">
         <v>1.4569686017619159</v>
       </c>
+      <c r="O6" s="15">
+        <v>1.4</v>
+      </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
